--- a/data/raw/2025/natcan6_070925.xlsx
+++ b/data/raw/2025/natcan6_070925.xlsx
@@ -18,7 +18,7 @@
     <sheet name="perpPara_090925" sheetId="4" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -688,6 +688,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/raw/2025/natcan6_070925.xlsx
+++ b/data/raw/2025/natcan6_070925.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lunduniversityo365-my.sharepoint.com/personal/an4718sc_lu_se/Documents/PhD/projects/dorsal_snapshot_discrimination_project/analysis/data/raw/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{1E442BC3-5649-E647-AE45-FD522DCC66E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{103D1FB8-3C53-0D45-81D1-9FD06FCC28AA}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{1E442BC3-5649-E647-AE45-FD522DCC66E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F85C03FA-9787-B54D-B8AA-14DEAB689969}"/>
   <bookViews>
-    <workbookView xWindow="6400" yWindow="1540" windowWidth="27640" windowHeight="16940" activeTab="2" xr2:uid="{357AECF0-BF18-3945-8EE9-9EEA9D4A9A12}"/>
+    <workbookView xWindow="780" yWindow="1400" windowWidth="27640" windowHeight="16940" activeTab="2" xr2:uid="{357AECF0-BF18-3945-8EE9-9EEA9D4A9A12}"/>
   </bookViews>
   <sheets>
     <sheet name="natcan6_070925" sheetId="2" r:id="rId1"/>
     <sheet name="natcan6_080925" sheetId="3" r:id="rId2"/>
-    <sheet name="perpPara_090925" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="160">
   <si>
     <t>1,0,1</t>
   </si>
@@ -519,120 +518,6 @@
   </si>
   <si>
     <t>46L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">notes: 
-This experiment followed on from the naturalistic canopy experiment to show that it isnt a matter of time of season / individual / setup that is causing the lack of  learning.
-Note that a mistake was made in trial 93 where the wrong stimulus was rewarded!
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,1,0 </t>
-  </si>
-  <si>
-    <t>0,0,0,1,0,1</t>
-  </si>
-  <si>
-    <t>1,1,0,1</t>
-  </si>
-  <si>
-    <t>123R</t>
-  </si>
-  <si>
-    <t>122L</t>
-  </si>
-  <si>
-    <t>121R</t>
-  </si>
-  <si>
-    <t>120L</t>
-  </si>
-  <si>
-    <t>119R</t>
-  </si>
-  <si>
-    <t>118L</t>
-  </si>
-  <si>
-    <t>117R</t>
-  </si>
-  <si>
-    <t>116R</t>
-  </si>
-  <si>
-    <t>115L</t>
-  </si>
-  <si>
-    <t>114R</t>
-  </si>
-  <si>
-    <t>113L</t>
-  </si>
-  <si>
-    <t>112R</t>
-  </si>
-  <si>
-    <t>111R</t>
-  </si>
-  <si>
-    <t>110L</t>
-  </si>
-  <si>
-    <t>109R</t>
-  </si>
-  <si>
-    <t>108L</t>
-  </si>
-  <si>
-    <t>107L</t>
-  </si>
-  <si>
-    <t>106R</t>
-  </si>
-  <si>
-    <t>105L</t>
-  </si>
-  <si>
-    <t>104L</t>
-  </si>
-  <si>
-    <t>103R</t>
-  </si>
-  <si>
-    <t>102R</t>
-  </si>
-  <si>
-    <t>101L</t>
-  </si>
-  <si>
-    <t>100R</t>
-  </si>
-  <si>
-    <t>99L</t>
-  </si>
-  <si>
-    <t>98R</t>
-  </si>
-  <si>
-    <t>97L</t>
-  </si>
-  <si>
-    <t>96R</t>
-  </si>
-  <si>
-    <t>95L</t>
-  </si>
-  <si>
-    <t>94R</t>
-  </si>
-  <si>
-    <t>93L</t>
-  </si>
-  <si>
-    <t>92R</t>
-  </si>
-  <si>
-    <t>91L</t>
   </si>
 </sst>
 </file>
@@ -668,11 +553,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2637,530 +2519,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDEFD3FE-5397-F448-B1B0-6964380A1E26}">
-  <dimension ref="A1:AH15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E1" t="s">
-        <v>193</v>
-      </c>
-      <c r="F1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G1" t="s">
-        <v>191</v>
-      </c>
-      <c r="H1" t="s">
-        <v>190</v>
-      </c>
-      <c r="I1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K1" t="s">
-        <v>187</v>
-      </c>
-      <c r="L1" t="s">
-        <v>186</v>
-      </c>
-      <c r="M1" t="s">
-        <v>185</v>
-      </c>
-      <c r="N1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O1" t="s">
-        <v>183</v>
-      </c>
-      <c r="P1" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>181</v>
-      </c>
-      <c r="R1" t="s">
-        <v>180</v>
-      </c>
-      <c r="S1" t="s">
-        <v>179</v>
-      </c>
-      <c r="T1" t="s">
-        <v>178</v>
-      </c>
-      <c r="U1" t="s">
-        <v>177</v>
-      </c>
-      <c r="V1" t="s">
-        <v>176</v>
-      </c>
-      <c r="W1" t="s">
-        <v>175</v>
-      </c>
-      <c r="X1" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>171</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>170</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>168</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>167</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>166</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>165</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="R2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-      <c r="U2">
-        <v>1</v>
-      </c>
-      <c r="V2" t="s">
-        <v>15</v>
-      </c>
-      <c r="W2">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA2">
-        <v>1</v>
-      </c>
-      <c r="AD2">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>22</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" t="s">
-        <v>163</v>
-      </c>
-      <c r="K3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" t="s">
-        <v>2</v>
-      </c>
-      <c r="O3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>1</v>
-      </c>
-      <c r="R3" t="s">
-        <v>2</v>
-      </c>
-      <c r="S3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U3" t="s">
-        <v>2</v>
-      </c>
-      <c r="V3" t="s">
-        <v>2</v>
-      </c>
-      <c r="W3" t="s">
-        <v>0</v>
-      </c>
-      <c r="X3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>25</v>
-      </c>
-      <c r="W4">
-        <v>1</v>
-      </c>
-      <c r="X4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>33</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>2</v>
-      </c>
-      <c r="H5" t="s">
-        <v>2</v>
-      </c>
-      <c r="I5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K5" t="s">
-        <v>2</v>
-      </c>
-      <c r="L5" t="s">
-        <v>111</v>
-      </c>
-      <c r="M5" t="s">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5" t="s">
-        <v>2</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5" t="s">
-        <v>20</v>
-      </c>
-      <c r="S5" t="s">
-        <v>2</v>
-      </c>
-      <c r="T5" t="s">
-        <v>2</v>
-      </c>
-      <c r="U5" t="s">
-        <v>2</v>
-      </c>
-      <c r="V5" t="s">
-        <v>0</v>
-      </c>
-      <c r="W5" t="s">
-        <v>2</v>
-      </c>
-      <c r="X5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>2</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>35</v>
-      </c>
-      <c r="AA6">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE6">
-        <v>1</v>
-      </c>
-      <c r="AF6">
-        <v>1</v>
-      </c>
-      <c r="AH6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" t="s">
-        <v>162</v>
-      </c>
-      <c r="H7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" t="s">
-        <v>2</v>
-      </c>
-      <c r="L7" t="s">
-        <v>20</v>
-      </c>
-      <c r="M7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N7" t="s">
-        <v>2</v>
-      </c>
-      <c r="O7" t="s">
-        <v>20</v>
-      </c>
-      <c r="P7" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>22</v>
-      </c>
-      <c r="R7" t="s">
-        <v>2</v>
-      </c>
-      <c r="S7" t="s">
-        <v>2</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="U7" t="s">
-        <v>2</v>
-      </c>
-      <c r="V7" t="s">
-        <v>22</v>
-      </c>
-      <c r="W7" t="s">
-        <v>2</v>
-      </c>
-      <c r="X7" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y7">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB7">
-        <v>1</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>161</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" ht="409.5" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4947ED-3964-404C-988D-B49CB88C2B13}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{7aa68094-6104-41a6-b443-d4b52451f617}" enabled="0" method="" siteId="{7aa68094-6104-41a6-b443-d4b52451f617}" removed="1"/>
+</clbl:labelList>
 </file>